--- a/backend/src/app/services/rule_engine/data/Bank_Eligibility_Matrix.xlsx
+++ b/backend/src/app/services/rule_engine/data/Bank_Eligibility_Matrix.xlsx
@@ -1005,7 +1005,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1140,6 +1140,11 @@
           <t>true</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>true</t>
@@ -1635,7 +1640,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1670,7 +1675,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>&lt; 5000</t>
+          <t>&lt; 10000</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">

--- a/backend/src/app/services/rule_engine/data/Bank_Eligibility_Matrix.xlsx
+++ b/backend/src/app/services/rule_engine/data/Bank_Eligibility_Matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:BS9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,6 +662,116 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>CIBIL PL Score</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>Age at Last EMI-Salaried</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Age at Last EMI-Self Employed</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>Resi-Cum-Office-Owned</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>Resi-Cum-Office-Both Rented</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Resi-Office-Separate-Both Rented</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Without a Guarantor</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>With a Guarantor</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>Rental Income-Agreement-No ITR-Not in Bank</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>Rental Income-Agreement-ITR-Not in Bank</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>Rental Income-Agreement-No ITR-In Bank</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>SE Current ITR</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>SE Previous ITR</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>Business ITR Years</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>HUF</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>Form 16 Years</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>Co-Applicant Age-Brother</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>Co-Applicant Age-Sister</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>Co-Applicant Income-Brother</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>Co-Applicant Income-Father</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Co-Applicant Income-Mother</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>Co-Applicant Income-Sister</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -809,6 +919,56 @@
           <t>BOI</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>&gt;= 701</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>&lt;= 60</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>&lt;= 65</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>&gt;= 300000</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>&gt;= 3</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -946,6 +1106,81 @@
           <t>Indian Bank</t>
         </is>
       </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>&lt;= 60</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>&lt;= 70</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>&gt;= 300000</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>&gt;= 300000</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1083,6 +1318,86 @@
           <t>IOB</t>
         </is>
       </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>&lt;= 75</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>&lt;= 75</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>&gt;= 300000</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>&gt;= 300000</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1220,6 +1535,71 @@
           <t>BOB</t>
         </is>
       </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>&lt;= 60</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>&lt;= 70</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>&gt;= 300000</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>&gt;= 1</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1357,6 +1737,26 @@
           <t>HDFC</t>
         </is>
       </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>&lt;= 70</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>&lt;= 70</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1494,6 +1894,26 @@
           <t>AXIS</t>
         </is>
       </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>&lt;= 70</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>&lt;= 70</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1631,6 +2051,31 @@
           <t>Kotak</t>
         </is>
       </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>&lt;= 70</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>&lt;= 70</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>&gt;= 100000</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1771,6 +2216,71 @@
       <c r="AV9" t="inlineStr">
         <is>
           <t>BOM</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>&lt;= 70</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>&lt;= 70</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>&gt;= 2</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
